--- a/data/Lüterkofen-Ichertswil/cost/total_demand.xlsx
+++ b/data/Lüterkofen-Ichertswil/cost/total_demand.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>54949.61672445336</v>
+        <v>2289.56736351889</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28119.90631628808</v>
+        <v>1171.66276317867</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>188315.2986053748</v>
+        <v>7846.470775223949</v>
       </c>
     </row>
   </sheetData>
